--- a/P13-portfolio professionnel de la data/livrables/Dashboard_Profil/Dashboard_Profil_LM.xlsx
+++ b/P13-portfolio professionnel de la data/livrables/Dashboard_Profil/Dashboard_Profil_LM.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5985c0986e4239b5/Formation DATA Analyst/P13-portfolio professionnel de la data/livrables/Dashboard_Profil/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_CA32BAD6F302B85C8931CD09D4DC0E6B6EDE9BDE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22922A9C-5BCE-4C33-9858-293605A52211}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projets" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Competences_Projets" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Soft_Skills" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Profil" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Projets" sheetId="1" r:id="rId1"/>
+    <sheet name="Competences_Projets" sheetId="2" r:id="rId2"/>
+    <sheet name="Soft_Skills" sheetId="3" r:id="rId3"/>
+    <sheet name="Profil" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,511 +28,547 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="165">
-  <si>
-    <t xml:space="preserve">Projet_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domaine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outil_Principal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duree_Heures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client_Fictif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contexte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL_GitHub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prise en main de la formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fondamentaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenClassrooms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Démarrage du parcours Data Analyst. Installation de l'environnement de travail et découverte des outils.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mise en place environnement Python/Jupyter, premiers repères data analyst, organisation de travail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://github.com/luxembourg64/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyse de ventes e-commerce (Excel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Grand Marché</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyste Data au service Marketing d'une entreprise de grande distribution. Analyse des ventes en ligne.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableaux croisés dynamiques, analyse exploratoire, visualisation Excel, synthèse commerciale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requêtes SQL — marché des assurances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL / BDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabinet d'assurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyse du marché des assurances habitation pour aider une compagnie à mieux accompagner ses clients.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requêtes SELECT, JOIN, GROUP BY, sous-requêtes, agrégations, filtres avancés.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Étude de santé publique — FAO (Python)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAO (Nations Unies)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission pour la Food and Agriculture Organization — étude mondiale sur l'alimentation et la sous-nutrition.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nettoyage de données, analyse exploratoire, statistiques descriptives, visualisation Matplotlib.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de données immobilière (SQL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laplace Immo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création d'un modèle de BDD pour prévoir le prix de vente des biens immobiliers (projet DATAImmo).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modélisation relationnelle, requêtes avancées, création de vues, clés étrangères.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion des données boutique (Python)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BottleNeck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission analyste chez un marchand de vin. Analyse des données et optimisation de la gestion des stocks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nettoyage et fusion de tables, gestion des doublons, détection d'anomalies stocks, Pandas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard suivi de projets (Power BI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data viz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power BI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanitoral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission de dataviz chez Sanitoral — tableau de bord de suivi de projets, coûts et performances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Strategy Canvas, modélisation données, KPIs, DAX, Power Query, visualisation interactive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Égalité F/H &amp; RGPD (KNIME)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KNIME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabinet de conseil RH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatisation du rapport annuel d'égalité professionnelle F/H en conformité RGPD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workflow KNIME (expérimental), indicateurs RH, conformité RGPD, export CSV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyse des ventes librairie (Python)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lapage Librairie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyse de l'activité d'une librairie ayant ouvert un site de vente en ligne il y a 2 ans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tests statistiques (Scipy), corrélations, analyse temporelle, visualisation avancée, Pandas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Étude accès eau potable (Power BI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONG DWFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission pour l'ONG DWFA — identifier les pays en difficulté d'accès à l'eau potable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicateurs géopolitiques, cartographie, storytelling données, DAX, Power Query.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Étude de marché internationale (Python)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Poule qui Chante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyse des marchés internationaux pour exporter des produits agroalimentaires biologiques.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clustering K-means, ACP, réduction de dimension, segmentation pays, Scikit-learn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Détection de faux billets (Python / ML)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONCFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Développement d'un modèle ML pour l'ONCFM — détection automatique de faux billets en euros.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Régression logistique, K-means, matrice de confusion, évaluation modèles, Scikit-learn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio professionnel data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion de projet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aéroworld / Data ESN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création d'un portfolio complet de consultant data — mission fictive pour Aéroworld.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion de projet, cahier des charges, veille technologique, communication professionnelle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Categorie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niveau_Etoiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niveau_Pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Langage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de données</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pandas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bibliothèque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scikit-learn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scipy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistiques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matplotlib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visualisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Query</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bureautique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K-means</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion projet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GitHub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versionning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soft_Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score_Pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Origine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curiosité intellectuelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formation data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exploration de domaines variés — santé publique, finance, agroalimentaire, aéronautique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rigueur analytique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formation data + expérience WM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Précision dans le traitement des données, vérification systématique des résultats.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conseil client</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expérience BNP Paribas / PwC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 ans d'accompagnement de clients Haute Valeur en ingénierie patrimoniale et fiscale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expérience WM + formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restitution claire de résultats complexes à des interlocuteurs non-techniques.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autonomie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conduite autonome de 12 projets en auto-formation sur 2 ans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Persévérance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintien de l'effort sur des projets longs et techniquement exigeants (90h+).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esprit critique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formation data + expérience juridique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questionnement des données, des hypothèses et des résultats de modèles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adaptabilité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconversion professionnelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passage du droit fiscal international à l'analyse de données — maîtrise de nouveaux outils.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laurent Maganto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titre_Actuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingénieur Patrimonial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employeur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BNP Paribas Wealth Management Luxembourg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst — OpenClassrooms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Localisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxembourg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nationalite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Française</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Langues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Français (natif) · Anglais (professionnel) · Espagnol (bon niveau)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annees_Exp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sustainability Essentials for Business Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certif_Org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cambridge Institute for Sustainability Leadership (CISL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certif_Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Décembre 2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.linkedin.com/in/laurentmaganto/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nb_Projets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total_Heures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nb_Domaines</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="178">
+  <si>
+    <t>Projet_ID</t>
+  </si>
+  <si>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Titre</t>
+  </si>
+  <si>
+    <t>Domaine</t>
+  </si>
+  <si>
+    <t>Outil_Principal</t>
+  </si>
+  <si>
+    <t>Duree_Heures</t>
+  </si>
+  <si>
+    <t>Rang</t>
+  </si>
+  <si>
+    <t>Client_Fictif</t>
+  </si>
+  <si>
+    <t>Contexte</t>
+  </si>
+  <si>
+    <t>Competences</t>
+  </si>
+  <si>
+    <t>URL_GitHub</t>
+  </si>
+  <si>
+    <t>P01</t>
+  </si>
+  <si>
+    <t>Prise en main de la formation</t>
+  </si>
+  <si>
+    <t>Fondamentaux</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>OpenClassrooms</t>
+  </si>
+  <si>
+    <t>Démarrage du parcours Data Analyst. Installation de l'environnement de travail et découverte des outils.</t>
+  </si>
+  <si>
+    <t>Mise en place environnement Python/Jupyter, premiers repères data analyst, organisation de travail.</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/</t>
+  </si>
+  <si>
+    <t>P02</t>
+  </si>
+  <si>
+    <t>Analyse de ventes e-commerce (Excel)</t>
+  </si>
+  <si>
+    <t>Business analysis</t>
+  </si>
+  <si>
+    <t>Excel</t>
+  </si>
+  <si>
+    <t>Le Grand Marché</t>
+  </si>
+  <si>
+    <t>Analyste Data au service Marketing d'une entreprise de grande distribution. Analyse des ventes en ligne.</t>
+  </si>
+  <si>
+    <t>Tableaux croisés dynamiques, analyse exploratoire, visualisation Excel, synthèse commerciale.</t>
+  </si>
+  <si>
+    <t>P03</t>
+  </si>
+  <si>
+    <t>Requêtes SQL — marché des assurances</t>
+  </si>
+  <si>
+    <t>SQL / BDD</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Cabinet d'assurance</t>
+  </si>
+  <si>
+    <t>Analyse du marché des assurances habitation pour aider une compagnie à mieux accompagner ses clients.</t>
+  </si>
+  <si>
+    <t>Requêtes SELECT, JOIN, GROUP BY, sous-requêtes, agrégations, filtres avancés.</t>
+  </si>
+  <si>
+    <t>P04</t>
+  </si>
+  <si>
+    <t>Étude de santé publique — FAO (Python)</t>
+  </si>
+  <si>
+    <t>FAO (Nations Unies)</t>
+  </si>
+  <si>
+    <t>Mission pour la Food and Agriculture Organization — étude mondiale sur l'alimentation et la sous-nutrition.</t>
+  </si>
+  <si>
+    <t>Nettoyage de données, analyse exploratoire, statistiques descriptives, visualisation Matplotlib.</t>
+  </si>
+  <si>
+    <t>P05</t>
+  </si>
+  <si>
+    <t>Base de données immobilière (SQL)</t>
+  </si>
+  <si>
+    <t>Laplace Immo</t>
+  </si>
+  <si>
+    <t>Création d'un modèle de BDD pour prévoir le prix de vente des biens immobiliers (projet DATAImmo).</t>
+  </si>
+  <si>
+    <t>Modélisation relationnelle, requêtes avancées, création de vues, clés étrangères.</t>
+  </si>
+  <si>
+    <t>P06</t>
+  </si>
+  <si>
+    <t>Gestion des données boutique (Python)</t>
+  </si>
+  <si>
+    <t>BottleNeck</t>
+  </si>
+  <si>
+    <t>Mission analyste chez un marchand de vin. Analyse des données et optimisation de la gestion des stocks.</t>
+  </si>
+  <si>
+    <t>Nettoyage et fusion de tables, gestion des doublons, détection d'anomalies stocks, Pandas.</t>
+  </si>
+  <si>
+    <t>P07</t>
+  </si>
+  <si>
+    <t>Dashboard suivi de projets (Power BI)</t>
+  </si>
+  <si>
+    <t>Data viz</t>
+  </si>
+  <si>
+    <t>Power BI</t>
+  </si>
+  <si>
+    <t>Sanitoral</t>
+  </si>
+  <si>
+    <t>Mission de dataviz chez Sanitoral — tableau de bord de suivi de projets, coûts et performances.</t>
+  </si>
+  <si>
+    <t>Product Strategy Canvas, modélisation données, KPIs, DAX, Power Query, visualisation interactive.</t>
+  </si>
+  <si>
+    <t>P08</t>
+  </si>
+  <si>
+    <t>Égalité F/H &amp; RGPD (KNIME)</t>
+  </si>
+  <si>
+    <t>KNIME</t>
+  </si>
+  <si>
+    <t>Cabinet de conseil RH</t>
+  </si>
+  <si>
+    <t>Automatisation du rapport annuel d'égalité professionnelle F/H en conformité RGPD.</t>
+  </si>
+  <si>
+    <t>Workflow KNIME (expérimental), indicateurs RH, conformité RGPD, export CSV.</t>
+  </si>
+  <si>
+    <t>P09</t>
+  </si>
+  <si>
+    <t>Analyse des ventes librairie (Python)</t>
+  </si>
+  <si>
+    <t>Lapage Librairie</t>
+  </si>
+  <si>
+    <t>Analyse de l'activité d'une librairie ayant ouvert un site de vente en ligne il y a 2 ans.</t>
+  </si>
+  <si>
+    <t>Tests statistiques (Scipy), corrélations, analyse temporelle, visualisation avancée, Pandas.</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>Étude accès eau potable (Power BI)</t>
+  </si>
+  <si>
+    <t>ONG DWFA</t>
+  </si>
+  <si>
+    <t>Mission pour l'ONG DWFA — identifier les pays en difficulté d'accès à l'eau potable.</t>
+  </si>
+  <si>
+    <t>Indicateurs géopolitiques, cartographie, storytelling données, DAX, Power Query.</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>Étude de marché internationale (Python)</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>La Poule qui Chante</t>
+  </si>
+  <si>
+    <t>Analyse des marchés internationaux pour exporter des produits agroalimentaires biologiques.</t>
+  </si>
+  <si>
+    <t>Clustering K-means, ACP, réduction de dimension, segmentation pays, Scikit-learn.</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>Détection de faux billets (Python / ML)</t>
+  </si>
+  <si>
+    <t>ONCFM</t>
+  </si>
+  <si>
+    <t>Développement d'un modèle ML pour l'ONCFM — détection automatique de faux billets en euros.</t>
+  </si>
+  <si>
+    <t>Régression logistique, K-means, matrice de confusion, évaluation modèles, Scikit-learn.</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>Portfolio professionnel data</t>
+  </si>
+  <si>
+    <t>Gestion de projet</t>
+  </si>
+  <si>
+    <t>Aéroworld / Data ESN</t>
+  </si>
+  <si>
+    <t>Création d'un portfolio complet de consultant data — mission fictive pour Aéroworld.</t>
+  </si>
+  <si>
+    <t>Gestion de projet, cahier des charges, veille technologique, communication professionnelle.</t>
+  </si>
+  <si>
+    <t>Outil</t>
+  </si>
+  <si>
+    <t>Categorie</t>
+  </si>
+  <si>
+    <t>Niveau_Etoiles</t>
+  </si>
+  <si>
+    <t>Niveau_Pct</t>
+  </si>
+  <si>
+    <t>Langage</t>
+  </si>
+  <si>
+    <t>Base de données</t>
+  </si>
+  <si>
+    <t>Pandas</t>
+  </si>
+  <si>
+    <t>Bibliothèque</t>
+  </si>
+  <si>
+    <t>Scikit-learn</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>Scipy</t>
+  </si>
+  <si>
+    <t>Statistiques</t>
+  </si>
+  <si>
+    <t>Matplotlib</t>
+  </si>
+  <si>
+    <t>Visualisation</t>
+  </si>
+  <si>
+    <t>DAX</t>
+  </si>
+  <si>
+    <t>Power Query</t>
+  </si>
+  <si>
+    <t>Bureautique</t>
+  </si>
+  <si>
+    <t>Workflow</t>
+  </si>
+  <si>
+    <t>K-means</t>
+  </si>
+  <si>
+    <t>ACP</t>
+  </si>
+  <si>
+    <t>Miro</t>
+  </si>
+  <si>
+    <t>Gestion projet</t>
+  </si>
+  <si>
+    <t>PowerPoint</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Versionning</t>
+  </si>
+  <si>
+    <t>Soft_Skill</t>
+  </si>
+  <si>
+    <t>Score_Pct</t>
+  </si>
+  <si>
+    <t>Origine</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Curiosité intellectuelle</t>
+  </si>
+  <si>
+    <t>Formation data</t>
+  </si>
+  <si>
+    <t>Exploration de domaines variés — santé publique, finance, agroalimentaire, aéronautique.</t>
+  </si>
+  <si>
+    <t>Rigueur analytique</t>
+  </si>
+  <si>
+    <t>Formation data + expérience WM</t>
+  </si>
+  <si>
+    <t>Précision dans le traitement des données, vérification systématique des résultats.</t>
+  </si>
+  <si>
+    <t>Conseil client</t>
+  </si>
+  <si>
+    <t>Expérience BNP Paribas / PwC</t>
+  </si>
+  <si>
+    <t>20 ans d'accompagnement de clients Haute Valeur en ingénierie patrimoniale et fiscale.</t>
+  </si>
+  <si>
+    <t>Expérience WM + formation</t>
+  </si>
+  <si>
+    <t>Restitution claire de résultats complexes à des interlocuteurs non-techniques.</t>
+  </si>
+  <si>
+    <t>Autonomie</t>
+  </si>
+  <si>
+    <t>Conduite autonome de 12 projets en auto-formation sur 2 ans.</t>
+  </si>
+  <si>
+    <t>Persévérance</t>
+  </si>
+  <si>
+    <t>Maintien de l'effort sur des projets longs et techniquement exigeants (90h+).</t>
+  </si>
+  <si>
+    <t>Esprit critique</t>
+  </si>
+  <si>
+    <t>Formation data + expérience juridique</t>
+  </si>
+  <si>
+    <t>Questionnement des données, des hypothèses et des résultats de modèles.</t>
+  </si>
+  <si>
+    <t>Adaptabilité</t>
+  </si>
+  <si>
+    <t>Reconversion professionnelle</t>
+  </si>
+  <si>
+    <t>Passage du droit fiscal international à l'analyse de données — maîtrise de nouveaux outils.</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Laurent Maganto</t>
+  </si>
+  <si>
+    <t>Titre_Actuel</t>
+  </si>
+  <si>
+    <t>Ingénieur Patrimonial</t>
+  </si>
+  <si>
+    <t>Employeur</t>
+  </si>
+  <si>
+    <t>BNP Paribas Wealth Management Luxembourg</t>
+  </si>
+  <si>
+    <t>Formation</t>
+  </si>
+  <si>
+    <t>Data Analyst — OpenClassrooms</t>
+  </si>
+  <si>
+    <t>Localisation</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Nationalite</t>
+  </si>
+  <si>
+    <t>Française</t>
+  </si>
+  <si>
+    <t>Langues</t>
+  </si>
+  <si>
+    <t>Français (natif) · Anglais (professionnel) · Espagnol (bon niveau)</t>
+  </si>
+  <si>
+    <t>Annees_Exp</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>Sustainability Essentials for Business Certificate</t>
+  </si>
+  <si>
+    <t>Certif_Org</t>
+  </si>
+  <si>
+    <t>Cambridge Institute for Sustainability Leadership (CISL)</t>
+  </si>
+  <si>
+    <t>Certif_Date</t>
+  </si>
+  <si>
+    <t>Décembre 2022</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/laurentmaganto/</t>
+  </si>
+  <si>
+    <t>Nb_Projets</t>
+  </si>
+  <si>
+    <t>Total_Heures</t>
+  </si>
+  <si>
+    <t>Nb_Domaines</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P01%20Prenez%20en%20main%20votre%20formation%20de%20Data%20Analyst</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P02-Faites%20une%20analyse%20de%20ventes%20pour%20un%20e-commerce%20(excel)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P03-requ%C3%AAtes%20SQL%20(BDD%20assurances)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P04-R%C3%A9alisez%20une%20%C3%A9tude%20de%20sant%C3%A9%20publique%20-%20FAO%20(Python)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P05-Base%20de%20donn%C3%A9es%20immobili%C3%A8re%20(SQL)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P06-Gestion%20des%20donn%C3%A9es%20boutique%20(Python)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P07-Dashboard%20suivi%20de%20projets%20(Power%20BI)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P08-%C3%A9galit%C3%A9%20F-H%20et%20RGPD%20(KNIME)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P09-Analysez%20des%20ventes%20librairie%20(Python)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P10-%C3%A9tude%20acc%C3%A8s%20eau%20potable%20(Power%20BI)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P11-%C3%A9tude%20de%20march%C3%A9%20internationale%20(Python)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P12-D%C3%A9tection%20faux%20billets%20(Python%20-%20ML)</t>
+  </si>
+  <si>
+    <t>https://github.com/luxembourg64/Formation-Data-Analyst-OpenClassrooms/tree/main/P13-portfolio%20professionnel%20de%20la%20data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,40 +577,30 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1A2E4A"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -606,14 +637,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -629,65 +660,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -746,47 +752,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1A2E4A"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -794,12 +816,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -828,7 +850,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -849,7 +871,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -900,7 +922,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -918,35 +940,34 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="45"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="10" width="60" customWidth="1"/>
+    <col min="11" max="11" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,11 +1002,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -997,10 +1018,10 @@
       <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -1012,15 +1033,15 @@
       <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K2" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1032,10 +1053,10 @@
       <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="3">
         <v>40</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="3">
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
@@ -1047,15 +1068,15 @@
       <c r="J3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K3" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1067,10 +1088,10 @@
       <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="2">
         <v>30</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="2">
         <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -1082,15 +1103,15 @@
       <c r="J4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K4" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1102,10 +1123,10 @@
       <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="3">
         <v>80</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="3">
         <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -1117,15 +1138,15 @@
       <c r="J5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K5" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="2">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1137,10 +1158,10 @@
       <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="2">
         <v>60</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2">
         <v>5</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -1152,15 +1173,15 @@
       <c r="J6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K6" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1172,10 +1193,10 @@
       <c r="E7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="3">
         <v>70</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="3">
         <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -1187,15 +1208,15 @@
       <c r="J7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K7" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="2">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1207,10 +1228,10 @@
       <c r="E8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="2">
         <v>60</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="2">
         <v>7</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -1222,15 +1243,15 @@
       <c r="J8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K8" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1242,10 +1263,10 @@
       <c r="E9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="3">
         <v>60</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="3">
         <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
@@ -1257,15 +1278,15 @@
       <c r="J9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K9" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1277,10 +1298,10 @@
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="2">
         <v>90</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="2">
         <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -1292,15 +1313,15 @@
       <c r="J10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K10" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1312,10 +1333,10 @@
       <c r="E11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="3">
         <v>70</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="3">
         <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -1327,15 +1348,15 @@
       <c r="J11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K11" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="2">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1347,10 +1368,10 @@
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="2">
         <v>90</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="2">
         <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -1362,15 +1383,15 @@
       <c r="J12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K12" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1382,10 +1403,10 @@
       <c r="E13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="3">
         <v>70</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="3">
         <v>12</v>
       </c>
       <c r="H13" s="3" t="s">
@@ -1397,15 +1418,15 @@
       <c r="J13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K13" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="2">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1417,10 +1438,10 @@
       <c r="E14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="2">
         <v>70</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="2">
         <v>13</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -1432,36 +1453,43 @@
       <c r="J14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>18</v>
+      <c r="K14" s="6" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{A39A428C-9C26-44A8-84EA-75757090D9C5}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{D3D1C825-F5B9-4097-9FD3-287AD16F7BCC}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{335D9649-F890-44AD-A30C-67C6D504B072}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{EA501E35-4F18-4820-B721-00B4DE7BD1CA}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{E1354589-39AC-442A-82E0-A520EB2981D6}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{D477C8E8-27EC-4E8F-8BBF-975216CC88FB}"/>
+    <hyperlink ref="K8" r:id="rId7" xr:uid="{1193D5CE-B6C2-4035-A7BB-90B9EE925050}"/>
+    <hyperlink ref="K9" r:id="rId8" xr:uid="{903FA0B5-65E8-4F8B-9A41-E48D1504AFA3}"/>
+    <hyperlink ref="K10" r:id="rId9" xr:uid="{62239F63-2173-4DEE-BE6E-65CDEB2C2621}"/>
+    <hyperlink ref="K11" r:id="rId10" xr:uid="{1CA7A408-AA65-4F74-9D87-2AB67B75DCC8}"/>
+    <hyperlink ref="K12" r:id="rId11" xr:uid="{079F38F3-3921-454B-BD9C-06C6BDA40132}"/>
+    <hyperlink ref="K13" r:id="rId12" xr:uid="{B0DD78C2-B7A6-4AF9-8C79-06B0553EBCA9}"/>
+    <hyperlink ref="K14" r:id="rId13" xr:uid="{2A2D818D-6D03-42C7-9D86-9711A19A510B}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1478,7 +1506,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -1488,14 +1516,14 @@
       <c r="C2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>43</v>
       </c>
@@ -1505,14 +1533,14 @@
       <c r="C3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="3">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="3">
         <v>85</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>61</v>
       </c>
@@ -1522,14 +1550,14 @@
       <c r="C4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>71</v>
       </c>
@@ -1539,14 +1567,14 @@
       <c r="C5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="3">
         <v>85</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>77</v>
       </c>
@@ -1556,14 +1584,14 @@
       <c r="C6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>82</v>
       </c>
@@ -1573,14 +1601,14 @@
       <c r="C7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="3">
         <v>85</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -1590,14 +1618,14 @@
       <c r="C8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>66</v>
       </c>
@@ -1607,14 +1635,14 @@
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="3">
         <v>4</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>82</v>
       </c>
@@ -1624,14 +1652,14 @@
       <c r="C10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>4</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -1641,14 +1669,14 @@
       <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="3">
         <v>3</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="3">
         <v>75</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -1658,14 +1686,14 @@
       <c r="C12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>3</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
@@ -1675,14 +1703,14 @@
       <c r="C13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="3">
         <v>4</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="3">
         <v>82</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
@@ -1692,14 +1720,14 @@
       <c r="C14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>61</v>
       </c>
@@ -1709,14 +1737,14 @@
       <c r="C15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="3">
         <v>4</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="3">
         <v>82</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>71</v>
       </c>
@@ -1726,14 +1754,14 @@
       <c r="C16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="2">
         <v>3</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="2">
         <v>65</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>77</v>
       </c>
@@ -1743,14 +1771,14 @@
       <c r="C17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="3">
         <v>3</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="3">
         <v>65</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>61</v>
       </c>
@@ -1760,14 +1788,14 @@
       <c r="C18" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2">
         <v>3</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
@@ -1777,14 +1805,14 @@
       <c r="C19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="3">
         <v>3</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="3">
         <v>72</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>61</v>
       </c>
@@ -1794,14 +1822,14 @@
       <c r="C20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="2">
         <v>3</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>48</v>
       </c>
@@ -1811,14 +1839,14 @@
       <c r="C21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="3">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="3">
         <v>68</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>66</v>
       </c>
@@ -1828,14 +1856,14 @@
       <c r="C22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="2">
         <v>3</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>48</v>
       </c>
@@ -1845,14 +1873,14 @@
       <c r="C23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="3">
         <v>4</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="3">
         <v>78</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>66</v>
       </c>
@@ -1862,14 +1890,14 @@
       <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="2">
         <v>4</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
@@ -1879,14 +1907,14 @@
       <c r="C25" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="3">
         <v>4</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -1896,14 +1924,14 @@
       <c r="C26" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
         <v>71</v>
       </c>
@@ -1913,14 +1941,14 @@
       <c r="C27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="3">
         <v>3</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="3">
         <v>65</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>77</v>
       </c>
@@ -1930,14 +1958,14 @@
       <c r="C28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="2">
         <v>3</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="2">
         <v>65</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
         <v>71</v>
       </c>
@@ -1947,14 +1975,14 @@
       <c r="C29" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="3">
         <v>3</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="3">
         <v>62</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>82</v>
       </c>
@@ -1964,14 +1992,14 @@
       <c r="C30" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="2">
         <v>3</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
         <v>82</v>
       </c>
@@ -1981,14 +2009,14 @@
       <c r="C31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="3">
         <v>4</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>82</v>
       </c>
@@ -1998,39 +2026,31 @@
       <c r="C32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="2">
         <v>3</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="2">
         <v>65</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>114</v>
       </c>
@@ -2044,11 +2064,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="2">
         <v>95</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2058,11 +2078,11 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="3">
         <v>92</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -2072,11 +2092,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="2">
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2086,11 +2106,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="3">
         <v>90</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -2100,11 +2120,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="2">
         <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2114,11 +2134,11 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="3">
         <v>88</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -2128,11 +2148,11 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="2">
         <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2142,11 +2162,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="3">
         <v>88</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -2157,29 +2177,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2199,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>141</v>
       </c>
@@ -2195,7 +2207,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>143</v>
       </c>
@@ -2203,7 +2215,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>145</v>
       </c>
@@ -2211,7 +2223,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>147</v>
       </c>
@@ -2219,7 +2231,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>149</v>
       </c>
@@ -2227,7 +2239,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>151</v>
       </c>
@@ -2235,15 +2247,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>154</v>
       </c>
@@ -2251,7 +2263,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>156</v>
       </c>
@@ -2259,7 +2271,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>158</v>
       </c>
@@ -2267,7 +2279,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>112</v>
       </c>
@@ -2275,7 +2287,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>160</v>
       </c>
@@ -2283,37 +2295,32 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="3">
         <v>734</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="3">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>